--- a/Har_Ghar_Solar_CRM.xlsx
+++ b/Har_Ghar_Solar_CRM.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Solar Leads" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,35 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00007A3D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00008000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +61,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -122,6 +154,25 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SolarLeads" displayName="SolarLeads" ref="A4:J6" headerRowCount="1">
+  <autoFilter ref="A4:J6"/>
+  <tableColumns count="10">
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="Customer Name"/>
+    <tableColumn id="3" name="Mobile Number"/>
+    <tableColumn id="4" name="City"/>
+    <tableColumn id="5" name="Monthly Bill"/>
+    <tableColumn id="6" name="Status"/>
+    <tableColumn id="7" name="Follow Note"/>
+    <tableColumn id="8" name="Follow Date"/>
+    <tableColumn id="9" name="Updated By"/>
+    <tableColumn id="10" name="Created Date"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -413,104 +464,208 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>☀ Har Ghar Solar CRM Report</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+    </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Customer Name</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Mobile</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Mobile Number</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Monthly Bill</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Follow Note</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Follow Date</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Updated By</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Lead Date</t>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Created Date</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>kaka</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>9368587694</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Moradabad</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>₹3000 - ₹5000</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Installed</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>SUMIT GIRI GOSWAMI</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>08077181038</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>CHANDAUSI</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>₹1000 - ₹3000</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Above ₹5000</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Contacted</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>nntnrtnrtnrtntrn</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:J1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/Har_Ghar_Solar_CRM.xlsx
+++ b/Har_Ghar_Solar_CRM.xlsx
@@ -595,7 +595,7 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">

--- a/Har_Ghar_Solar_CRM.xlsx
+++ b/Har_Ghar_Solar_CRM.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,19 +28,38 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="18"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00005B38"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00005B38"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -49,7 +68,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00008000"/>
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B5E20"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F8F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3E5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0F2F1"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,14 +120,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -157,21 +229,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SolarLeads" displayName="SolarLeads" ref="A4:J6" headerRowCount="1">
-  <autoFilter ref="A4:J6"/>
-  <tableColumns count="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SolarLeads" displayName="SolarLeads" ref="A6:L10" headerRowCount="1">
+  <autoFilter ref="A6:L10"/>
+  <tableColumns count="12">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Customer Name"/>
     <tableColumn id="3" name="Mobile Number"/>
     <tableColumn id="4" name="City"/>
-    <tableColumn id="5" name="Monthly Bill"/>
-    <tableColumn id="6" name="Status"/>
-    <tableColumn id="7" name="Follow Note"/>
-    <tableColumn id="8" name="Follow Date"/>
-    <tableColumn id="9" name="Updated By"/>
-    <tableColumn id="10" name="Created Date"/>
+    <tableColumn id="5" name="District"/>
+    <tableColumn id="6" name="Monthly Bill"/>
+    <tableColumn id="7" name="Status"/>
+    <tableColumn id="8" name="Assigned Vendor"/>
+    <tableColumn id="9" name="Follow Note"/>
+    <tableColumn id="10" name="Follow Date"/>
+    <tableColumn id="11" name="Updated By"/>
+    <tableColumn id="12" name="Created Date"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -464,204 +538,327 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>☀ Har Ghar Solar CRM Report</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
+          <t>HAR GHAR SOLAR — CRM Report</t>
+        </is>
+      </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Generated: 11-07-2026 16:38  |  Total Leads: 4</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>New: 0  |  Assigned: 0  |  Contacted: 0  |  Site Visit: 1  |  Quotation Sent: 1  |  Installation: 1  |  Completed: 1  |  Cancelled: 0</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Customer Name</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Mobile Number</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Monthly Bill</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Vendor</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>Follow Note</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>Follow Date</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>Updated By</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>SUMIT GIRI GOSWAMI</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>08077181038</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>CHANDAUSI</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Sambhal</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Above ₹5000</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Site Visit</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Shiv Computer</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>SUMIT GIRI GOSWAMI</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>08077181038</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>CHANDAUSI</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Sambhal</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Above ₹5000</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Shiv Computer</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr"/>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>kaka</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>9368587694</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Moradabad</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>₹3000 - ₹5000</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Installed</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>Quotation Sent</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Kunwar singh</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>ok boss</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>9090909090</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>SUMIT GIRI GOSWAMI</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>08077181038</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>CHANDAUSI</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Above ₹5000</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr"/>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>nntnrtnrtnrtntrn</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>SUMIT GIRI GOSWAMI</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>08077181038</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>CHANDAUSI</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Above ₹5000</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Contacted</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>nntnrtnrtnrtntrn</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+  <mergeCells count="4">
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A4:L4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/Har_Ghar_Solar_CRM.xlsx
+++ b/Har_Ghar_Solar_CRM.xlsx
@@ -83,22 +83,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF9C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F3E5F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C8E6C9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3E0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E0F2F1"/>
       </patternFill>
     </fill>
   </fills>
@@ -229,8 +229,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SolarLeads" displayName="SolarLeads" ref="A6:L10" headerRowCount="1">
-  <autoFilter ref="A6:L10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SolarLeads" displayName="SolarLeads" ref="A6:L17" headerRowCount="1">
+  <autoFilter ref="A6:L17"/>
   <tableColumns count="12">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Customer Name"/>
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -565,14 +565,14 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 11-07-2026 16:38  |  Total Leads: 4</t>
+          <t>Generated: 11-07-2026 20:15  |  Total Leads: 11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>New: 0  |  Assigned: 0  |  Contacted: 0  |  Site Visit: 1  |  Quotation Sent: 1  |  Installation: 1  |  Completed: 1  |  Cancelled: 0</t>
+          <t>New: 2  |  Assigned: 5  |  Contacted: 0  |  Site Visit: 1  |  Quotation Sent: 0  |  Installation: 0  |  Completed: 3  |  Cancelled: 0</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>08077181038</t>
+          <t>+918077181038</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Sambhal</t>
+          <t>Basti</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Site Visit</t>
+          <t>Assigned</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -695,7 +695,7 @@
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>08077181038</t>
+          <t>+918077181038</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Sambhal</t>
+          <t>Basti</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -724,21 +724,13 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>Shiv Computer</t>
-        </is>
-      </c>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr"/>
       <c r="I8" s="7" t="inlineStr"/>
       <c r="J8" s="7" t="inlineStr"/>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
+      <c r="K8" s="7" t="inlineStr"/>
       <c r="L8" s="7" t="inlineStr">
         <is>
           <t>2026-07-11</t>
@@ -747,107 +739,483 @@
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>kaka</t>
+          <t>SUMIT GIRI GOSWAMI</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>9368587694</t>
+          <t>+918077181038</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Moradabad</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr"/>
+          <t>CHANDAUSI</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Basti</t>
+        </is>
+      </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>₹3000 - ₹5000</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>Quotation Sent</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>Kunwar singh</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>ok boss</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
+          <t>Above ₹5000</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>9090909090</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Latha Jayaprakash</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>8080808080</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>laddakh</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Saharanpur</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>₹1000 - ₹3000</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>Shiv Computer</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr"/>
+      <c r="J10" s="7" t="inlineStr"/>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>klklklklk</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>909090090</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>CHANDAUSI</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Bhadohi</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>₹3000 - ₹5000</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Kunwar singh</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>55555555</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Chanduasi</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Bhadohi</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>₹3000 - ₹5000</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Shiv Computer</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr"/>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>SUMIT GIRI GOSWAMI</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>77888877884845120</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>CHANDAUSI</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Bijnor</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Below ₹1000</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>Site Visit</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Kunwar singh</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>SUMIT GIRI GOSWAMI</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>08077181038</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>CHANDAUSI</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Sambhal</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Above ₹5000</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>Shiv Computer</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr"/>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>kaka@gmail.com</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>SUMIT GIRI GOSWAMI</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>08077181038</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>CHANDAUSI</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Sambhal</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Above ₹5000</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Shiv Computer</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>ou7tfuygh 8gyobi uhb87 guibjk</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>kaka</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>9368587694</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Moradabad</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr"/>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>₹3000 - ₹5000</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Kunwar singh</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>ok boss</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>SUMIT GIRI GOSWAMI</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>08077181038</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>CHANDAUSI</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Above ₹5000</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>Installation</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr"/>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Shiv Computer</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>nntnrtnrtnrtntrn</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="K10" s="7" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="L10" s="7" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>

--- a/Har_Ghar_Solar_CRM.xlsx
+++ b/Har_Ghar_Solar_CRM.xlsx
@@ -83,22 +83,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E3F2FD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF9C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00F3E5F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0F2F1"/>
       </patternFill>
     </fill>
   </fills>
@@ -229,8 +229,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SolarLeads" displayName="SolarLeads" ref="A6:L17" headerRowCount="1">
-  <autoFilter ref="A6:L17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SolarLeads" displayName="SolarLeads" ref="A6:L10" headerRowCount="1">
+  <autoFilter ref="A6:L10"/>
   <tableColumns count="12">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Customer Name"/>
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -565,14 +565,14 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 11-07-2026 20:15  |  Total Leads: 11</t>
+          <t>Generated: 11-07-2026 16:38  |  Total Leads: 4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>New: 2  |  Assigned: 5  |  Contacted: 0  |  Site Visit: 1  |  Quotation Sent: 0  |  Installation: 0  |  Completed: 3  |  Cancelled: 0</t>
+          <t>New: 0  |  Assigned: 0  |  Contacted: 0  |  Site Visit: 1  |  Quotation Sent: 1  |  Installation: 1  |  Completed: 1  |  Cancelled: 0</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>+918077181038</t>
+          <t>08077181038</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Basti</t>
+          <t>Sambhal</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Assigned</t>
+          <t>Site Visit</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -695,7 +695,7 @@
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="7" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>+918077181038</t>
+          <t>08077181038</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Basti</t>
+          <t>Sambhal</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -724,13 +724,21 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr"/>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Shiv Computer</t>
+        </is>
+      </c>
       <c r="I8" s="7" t="inlineStr"/>
       <c r="J8" s="7" t="inlineStr"/>
-      <c r="K8" s="7" t="inlineStr"/>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
           <t>2026-07-11</t>
@@ -739,483 +747,107 @@
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>SUMIT GIRI GOSWAMI</t>
+          <t>kaka</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>+918077181038</t>
+          <t>9368587694</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>CHANDAUSI</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Basti</t>
-        </is>
-      </c>
+          <t>Moradabad</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Above ₹5000</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr"/>
-      <c r="K9" s="5" t="inlineStr"/>
+          <t>₹3000 - ₹5000</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>Quotation Sent</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Kunwar singh</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>ok boss</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>9090909090</t>
+        </is>
+      </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Latha Jayaprakash</t>
+          <t>SUMIT GIRI GOSWAMI</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>8080808080</t>
+          <t>08077181038</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>laddakh</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Saharanpur</t>
-        </is>
-      </c>
+          <t>CHANDAUSI</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr"/>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>₹1000 - ₹3000</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Assigned</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>Shiv Computer</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr"/>
-      <c r="J10" s="7" t="inlineStr"/>
+          <t>Above ₹5000</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr"/>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>nntnrtnrtnrtntrn</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>klklklklk</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>909090090</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>CHANDAUSI</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Bhadohi</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>₹3000 - ₹5000</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Assigned</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>Kunwar singh</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>55555555</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Chanduasi</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Bhadohi</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>₹3000 - ₹5000</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Assigned</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>Shiv Computer</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr"/>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>SUMIT GIRI GOSWAMI</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>77888877884845120</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>CHANDAUSI</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Bijnor</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Below ₹1000</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>Site Visit</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>Kunwar singh</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>SUMIT GIRI GOSWAMI</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>08077181038</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>CHANDAUSI</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>Sambhal</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>Above ₹5000</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Assigned</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>Shiv Computer</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr"/>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="inlineStr">
-        <is>
-          <t>kaka@gmail.com</t>
-        </is>
-      </c>
-      <c r="L14" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>SUMIT GIRI GOSWAMI</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>08077181038</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>CHANDAUSI</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Sambhal</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Above ₹5000</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>Shiv Computer</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>ou7tfuygh 8gyobi uhb87 guibjk</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr"/>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>kaka</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>9368587694</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Moradabad</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr"/>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>₹3000 - ₹5000</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>Kunwar singh</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>ok boss</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>SUMIT GIRI GOSWAMI</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>08077181038</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>CHANDAUSI</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>Above ₹5000</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>Shiv Computer</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>nntnrtnrtnrtntrn</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>

--- a/Har_Ghar_Solar_CRM.xlsx
+++ b/Har_Ghar_Solar_CRM.xlsx
@@ -49,7 +49,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -83,22 +83,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3E5F5"/>
+        <fgColor rgb="00E3F2FD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C8E6C9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3E0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E0F2F1"/>
       </patternFill>
     </fill>
   </fills>
@@ -120,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -144,12 +134,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -229,8 +213,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SolarLeads" displayName="SolarLeads" ref="A6:L10" headerRowCount="1">
-  <autoFilter ref="A6:L10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SolarLeads" displayName="SolarLeads" ref="A6:L18" headerRowCount="1">
+  <autoFilter ref="A6:L18"/>
   <tableColumns count="12">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Customer Name"/>
@@ -538,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -565,14 +549,14 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 11-07-2026 16:38  |  Total Leads: 4</t>
+          <t>Generated: 13-07-2026 22:30  |  Total Leads: 12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>New: 0  |  Assigned: 0  |  Contacted: 0  |  Site Visit: 1  |  Quotation Sent: 1  |  Installation: 1  |  Completed: 1  |  Cancelled: 0</t>
+          <t>New: 0  |  Assigned: 2  |  Contacted: 0  |  Site Visit: 0  |  Quotation Sent: 0  |  Installation: 0  |  Completed: 10  |  Cancelled: 0</t>
         </is>
       </c>
     </row>
@@ -643,7 +627,7 @@
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -652,7 +636,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>08077181038</t>
+          <t>+918077181038</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -662,26 +646,30 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Sambhal</t>
+          <t>Bareilly</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Above ₹5000</t>
+          <t>₹1000 - ₹3000</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Site Visit</t>
+          <t>Assigned</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>Shiv Computer</t>
+          <t>UNIVERSAL ENTERPRISES</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
           <t>admin</t>
@@ -695,7 +683,7 @@
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="7" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
@@ -704,7 +692,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>08077181038</t>
+          <t>+918077181038</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -714,7 +702,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Sambhal</t>
+          <t>Basti</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -733,7 +721,11 @@
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr"/>
-      <c r="J8" s="7" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
           <t>admin</t>
@@ -747,107 +739,551 @@
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>kaka</t>
+          <t>SUMIT GIRI GOSWAMI</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>9368587694</t>
+          <t>+918077181038</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Moradabad</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr"/>
+          <t>CHANDAUSI</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Basti</t>
+        </is>
+      </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>₹3000 - ₹5000</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>Quotation Sent</t>
+          <t>Above ₹5000</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>Kunwar singh</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>ok boss</t>
-        </is>
-      </c>
+          <t>Shiv Computer</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr"/>
       <c r="J9" s="5" t="inlineStr">
         <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
           <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>9090909090</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>SUMIT GIRI GOSWAMI</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>+918077181038</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>CHANDAUSI</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Basti</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Above ₹5000</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>Kunwar singh</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr"/>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Latha Jayaprakash</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>8080808080</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>laddakh</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Saharanpur</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>₹1000 - ₹3000</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Raghav Enterprises</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>klklklklk</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>909090090</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>CHANDAUSI</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Bhadohi</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>₹3000 - ₹5000</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Kunwar singh</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr"/>
+      <c r="J12" s="7" t="inlineStr"/>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>55555555</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Chanduasi</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Bhadohi</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>₹3000 - ₹5000</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Shiv Computer</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>SUMIT GIRI GOSWAMI</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>77888877884845120</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>CHANDAUSI</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Bijnor</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Below ₹1000</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>Kunwar singh</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr"/>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>SUMIT GIRI GOSWAMI</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>08077181038</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>CHANDAUSI</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Sambhal</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Above ₹5000</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Shiv Computer</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>SUMIT GIRI GOSWAMI</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>08077181038</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>CHANDAUSI</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Sambhal</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Above ₹5000</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Shiv Computer</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>ou7tfuygh 8gyobi uhb87 guibjk</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr"/>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>kaka</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>9368587694</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Moradabad</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>₹3000 - ₹5000</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Kunwar singh</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>ok boss</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>SUMIT GIRI GOSWAMI</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>08077181038</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>CHANDAUSI</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr"/>
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>Above ₹5000</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>Installation</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr"/>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Shiv Computer</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>nntnrtnrtnrtntrn</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="K10" s="7" t="inlineStr">
+      <c r="K18" s="7" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="L10" s="7" t="inlineStr">
+      <c r="L18" s="7" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>

--- a/Har_Ghar_Solar_CRM.xlsx
+++ b/Har_Ghar_Solar_CRM.xlsx
@@ -49,7 +49,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -83,12 +83,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E3F2FD"/>
+        <fgColor rgb="00F3E5F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0F2F1"/>
       </patternFill>
     </fill>
   </fills>
@@ -110,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -134,6 +144,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -213,8 +229,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SolarLeads" displayName="SolarLeads" ref="A6:L18" headerRowCount="1">
-  <autoFilter ref="A6:L18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SolarLeads" displayName="SolarLeads" ref="A6:L10" headerRowCount="1">
+  <autoFilter ref="A6:L10"/>
   <tableColumns count="12">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Customer Name"/>
@@ -522,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -549,14 +565,14 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 13-07-2026 22:30  |  Total Leads: 12</t>
+          <t>Generated: 11-07-2026 16:38  |  Total Leads: 4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>New: 0  |  Assigned: 2  |  Contacted: 0  |  Site Visit: 0  |  Quotation Sent: 0  |  Installation: 0  |  Completed: 10  |  Cancelled: 0</t>
+          <t>New: 0  |  Assigned: 0  |  Contacted: 0  |  Site Visit: 1  |  Quotation Sent: 1  |  Installation: 1  |  Completed: 1  |  Cancelled: 0</t>
         </is>
       </c>
     </row>
@@ -627,7 +643,7 @@
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -636,7 +652,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>+918077181038</t>
+          <t>08077181038</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -646,30 +662,26 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Bareilly</t>
+          <t>Sambhal</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>₹1000 - ₹3000</t>
+          <t>Above ₹5000</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Assigned</t>
+          <t>Site Visit</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>UNIVERSAL ENTERPRISES</t>
+          <t>Shiv Computer</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
+      <c r="J7" s="5" t="inlineStr"/>
       <c r="K7" s="5" t="inlineStr">
         <is>
           <t>admin</t>
@@ -683,7 +695,7 @@
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="7" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
@@ -692,7 +704,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>+918077181038</t>
+          <t>08077181038</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -702,7 +714,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Basti</t>
+          <t>Sambhal</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -721,11 +733,7 @@
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr"/>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
+      <c r="J8" s="7" t="inlineStr"/>
       <c r="K8" s="7" t="inlineStr">
         <is>
           <t>admin</t>
@@ -739,63 +747,63 @@
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>SUMIT GIRI GOSWAMI</t>
+          <t>kaka</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>+918077181038</t>
+          <t>9368587694</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>CHANDAUSI</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Basti</t>
-        </is>
-      </c>
+          <t>Moradabad</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Above ₹5000</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>Completed</t>
+          <t>₹3000 - ₹5000</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>Quotation Sent</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>Shiv Computer</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr"/>
+          <t>Kunwar singh</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>ok boss</t>
+        </is>
+      </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>9090909090</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="7" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
@@ -804,7 +812,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>+918077181038</t>
+          <t>08077181038</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -812,30 +820,26 @@
           <t>CHANDAUSI</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Basti</t>
-        </is>
-      </c>
+      <c r="E10" s="7" t="inlineStr"/>
       <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Above ₹5000</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>Kunwar singh</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr"/>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr"/>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>nntnrtnrtnrtntrn</t>
+        </is>
+      </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -844,446 +848,6 @@
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Latha Jayaprakash</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>8080808080</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>laddakh</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Saharanpur</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>₹1000 - ₹3000</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Assigned</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>Raghav Enterprises</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>klklklklk</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>909090090</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>CHANDAUSI</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Bhadohi</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>₹3000 - ₹5000</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>Kunwar singh</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr"/>
-      <c r="J12" s="7" t="inlineStr"/>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>55555555</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Chanduasi</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Bhadohi</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>₹3000 - ₹5000</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>Shiv Computer</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>SUMIT GIRI GOSWAMI</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>77888877884845120</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>CHANDAUSI</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>Bijnor</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>Below ₹1000</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>Kunwar singh</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr"/>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="L14" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>SUMIT GIRI GOSWAMI</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>08077181038</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>CHANDAUSI</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Sambhal</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Above ₹5000</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>Shiv Computer</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>SUMIT GIRI GOSWAMI</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>08077181038</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>CHANDAUSI</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>Sambhal</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>Above ₹5000</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>Shiv Computer</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>ou7tfuygh 8gyobi uhb87 guibjk</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr"/>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>kaka</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>9368587694</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Moradabad</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>₹3000 - ₹5000</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>Kunwar singh</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>ok boss</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>SUMIT GIRI GOSWAMI</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>08077181038</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>CHANDAUSI</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr"/>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>Above ₹5000</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>Shiv Computer</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>nntnrtnrtnrtntrn</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>

--- a/Har_Ghar_Solar_CRM.xlsx
+++ b/Har_Ghar_Solar_CRM.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Solar Leads" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Solar Leads" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -49,7 +52,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -78,27 +81,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F1F8F4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F3E5F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3E0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E0F2F1"/>
+        <fgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -120,36 +103,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -229,8 +203,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SolarLeads" displayName="SolarLeads" ref="A6:L10" headerRowCount="1">
-  <autoFilter ref="A6:L10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SolarLeads" displayName="SolarLeads" ref="A6:L7" headerRowCount="1">
+  <autoFilter ref="A6:L7"/>
   <tableColumns count="12">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Customer Name"/>
@@ -538,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -556,23 +530,23 @@
   </cols>
   <sheetData>
     <row r="1" ht="35" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>HAR GHAR SOLAR — CRM Report</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Generated: 11-07-2026 16:38  |  Total Leads: 4</t>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Generated: 23-07-2026 10:14  |  Total Leads: 1</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>New: 0  |  Assigned: 0  |  Contacted: 0  |  Site Visit: 1  |  Quotation Sent: 1  |  Installation: 1  |  Completed: 1  |  Cancelled: 0</t>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>New: 1  |  Assigned: 0  |  Contacted: 0  |  Site Visit: 0  |  Quotation Sent: 0  |  Installation: 0  |  Completed: 0  |  Cancelled: 0</t>
         </is>
       </c>
     </row>
@@ -580,276 +554,108 @@
       <c r="A4" t="inlineStr"/>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Customer Name</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Mobile Number</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>District</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Monthly Bill</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Assigned Vendor</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>Follow Note</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Follow Date</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>Updated By</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>SUMIT GIRI GOSWAMI</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>08077181038</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>+918077181038</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>CHANDAUSI</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Sambhal</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Above ₹5000</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Site Visit</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>Shiv Computer</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="5" t="inlineStr"/>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>SUMIT GIRI GOSWAMI</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>08077181038</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>CHANDAUSI</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Sambhal</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>Above ₹5000</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>Shiv Computer</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr"/>
-      <c r="J8" s="7" t="inlineStr"/>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>kaka</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>9368587694</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Moradabad</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Basti</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>₹3000 - ₹5000</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>Quotation Sent</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>Kunwar singh</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>ok boss</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>9090909090</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>SUMIT GIRI GOSWAMI</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>08077181038</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>CHANDAUSI</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>Above ₹5000</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>Installation</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr"/>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>nntnrtnrtnrtntrn</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="L10" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr"/>
+      <c r="K7" s="6" t="inlineStr"/>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
